--- a/reports/二级子公司C_利润表_2025-07.xlsx
+++ b/reports/二级子公司C_利润表_2025-07.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>98234022</v>
+        <v>101351926</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>95367201</v>
+        <v>96288413</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>594245114</v>
+        <v>593829379</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>450126</v>
+        <v>446515</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2774852</v>
+        <v>2777301</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>394287</v>
+        <v>390011</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2428327</v>
+        <v>2429943</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>337981</v>
+        <v>334004</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2081807</v>
+        <v>2082497</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>315143</v>
+        <v>311793</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1943410</v>
+        <v>1943293</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>168517</v>
+        <v>167232</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1041300</v>
+        <v>1040841</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>134493</v>
+        <v>134054</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>833151</v>
+        <v>832529</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>96433475</v>
+        <v>99568317</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>93566654</v>
+        <v>94504804</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>89108893</v>
+        <v>89994742</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>555391014</v>
+        <v>554959630</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1335936</v>
+        <v>1351646</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>8329474</v>
+        <v>8325413</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>891105</v>
+        <v>901350</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>5551884</v>
+        <v>5551255</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3346679</v>
+        <v>3377478</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>20815513</v>
+        <v>20821386</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>447208</v>
+        <v>449576</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>2774967</v>
+        <v>2776708</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>336248</v>
+        <v>336408</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>2081037</v>
+        <v>2082830</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>561745</v>
+        <v>559271</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>3468361</v>
+        <v>3471641</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>675323</v>
+        <v>669588</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>4162338</v>
+        <v>4165929</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2816530</v>
+        <v>2785311</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>17345573</v>
+        <v>17356451</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>50291</v>
+        <v>49701</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>349915</v>
+        <v>350113</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1336394</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>8328176</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>892107</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>5551015</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>66620028</v>
+        <v>71867353</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>59329351</v>
+        <v>59744793</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>57992890</v>
+        <v>58394573</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>361039014</v>
+        <v>360707619</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1336461</v>
+        <v>1350220</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>8330705</v>
+        <v>8324495</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2252963</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>13875978</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>721049</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>4441121</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>450251</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2776258</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>539341</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>3332124</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>403556</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2499432</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>268362</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1666393</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>223137</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1388633</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1014002</v>
+        <v>1002555</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>6244551</v>
+        <v>6248213</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>788495</v>
+        <v>779298</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>4857808</v>
+        <v>4858929</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>675026</v>
+        <v>668278</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>4164665</v>
+        <v>4163975</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>5052500</v>
+        <v>5019312</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>31240332</v>
+        <v>31223694</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>200004</v>
+        <v>223563</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1400290</v>
+        <v>1387497</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>349145</v>
+        <v>350193</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2450770</v>
+        <v>2449423</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>398210</v>
+        <v>350193</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2801023</v>
+        <v>2449423</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>49714</v>
+        <v>50242</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>350123</v>
+        <v>349871</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>181056</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1259570</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>394300</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2428803</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>120580</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>839898</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>90265</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>630019</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>150082</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1050188</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>558907</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>3471660</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>79671</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>560203</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>59668</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>420151</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>99400</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>700209</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>69622</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>490090</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>49807</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>350012</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>39935</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>279967</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>30027</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>209948</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>29813447</v>
+        <v>29033859</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>34835560</v>
+        <v>32750476</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>225328</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1387660</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>50289</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>349915</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>79748</v>
+        <v>80370</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>559991</v>
+        <v>559943</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>29733699</v>
+        <v>29178817</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2804839</v>
+        <v>2800589</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>19594366</v>
+        <v>19603877</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>26928860</v>
+        <v>26378228</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>26928860</v>
+        <v>26378228</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>26928860</v>
+        <v>26378228</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>26928860</v>
+        <v>26378228</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>26928860</v>
+        <v>26378228</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
